--- a/holiday_forms/004_holiday_party_food_preferences--holiday_forms.xlsx
+++ b/holiday_forms/004_holiday_party_food_preferences--holiday_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -735,8 +735,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -764,12 +764,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'attending',_'value':_'attending'}</t>
+          <t>attending</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'attending', 'value': 'Attending'}</t>
+          <t>Attending</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'not_attending',_'value':_'not_attending'}</t>
+          <t>not_attending</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'not_attending', 'value': 'Not attending'}</t>
+          <t>Not attending</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'vegetarian',_'value':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'vegetarian', 'value': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'vegan',_'value':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'vegan', 'value': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'gluten_free',_'value':_'gluten-free'}</t>
+          <t>gluten-free</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'gluten_free', 'value': 'Gluten-free'}</t>
+          <t>Gluten-free</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'dairy_free',_'value':_'dairy-free'}</t>
+          <t>dairy-free</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'dairy_free', 'value': 'Dairy-free'}</t>
+          <t>Dairy-free</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'peanuts',_'value':_'peanuts'}</t>
+          <t>peanuts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'peanuts', 'value': 'Peanuts'}</t>
+          <t>Peanuts</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'shellfish',_'value':_'shellfish'}</t>
+          <t>shellfish</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'shellfish', 'value': 'Shellfish'}</t>
+          <t>Shellfish</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'soy',_'value':_'soy'}</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'soy', 'value': 'Soy'}</t>
+          <t>Soy</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'mexican',_'value':_'mexican'}</t>
+          <t>mexican</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'mexican', 'value': 'Mexican'}</t>
+          <t>Mexican</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'italian',_'value':_'italian'}</t>
+          <t>italian</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'italian', 'value': 'Italian'}</t>
+          <t>Italian</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'chinese',_'value':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'chinese', 'value': 'Chinese'}</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
